--- a/zy70942/reconciliation_summary_BATCH_20260527_001.xlsx
+++ b/zy70942/reconciliation_summary_BATCH_20260527_001.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26 16:48:52</t>
+          <t>2026-05-26 17:10:48</t>
         </is>
       </c>
     </row>
